--- a/知识库Excel模板.xlsx
+++ b/知识库Excel模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="完整知识库展示模板" sheetId="5" r:id="rId1"/>
@@ -1727,8 +1727,8 @@
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="7" max="7" width="53.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
     <col min="9" max="10" width="23" customWidth="1"/>
     <col min="11" max="14" width="12" customWidth="1"/>
   </cols>
